--- a/data/600686_金龙汽车_财务数据.xlsx
+++ b/data/600686_金龙汽车_财务数据.xlsx
@@ -11799,7 +11799,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -19451,7 +19451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19481,8 +19481,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19529,22 +19527,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -19554,75 +19552,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -19656,58 +19644,52 @@
         <v>4.850416755823366</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>-0.3628453477939307</v>
+      <c r="J2" s="3" t="n">
+        <v>82.34616911472806</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>82.34616911472806</v>
+        <v>1.222994210090984</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.222994210090984</v>
+        <v>1.143810311552247</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1.143810311552247</v>
+        <v>466.4492916572971</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>1.710655304202194</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>210.4456690460471</v>
-      </c>
-      <c r="P2" s="3" t="n">
         <v>16.34194462451254</v>
       </c>
-      <c r="Q2" s="3" t="n">
-        <v>22.02920204857434</v>
-      </c>
-      <c r="R2" s="6" t="n">
+      <c r="P2" s="6" t="n">
         <v>0.8665328178491465</v>
       </c>
-      <c r="S2" s="6" t="n">
+      <c r="Q2" s="6" t="n">
         <v>0.9841724911682221</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="V2" s="6" t="n">
+        <v>0.9063538970911763</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>-2070000000</v>
+      </c>
       <c r="X2" s="6" t="n">
-        <v>0.9063538970911763</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>-2070000000</v>
-      </c>
-      <c r="Z2" s="6" t="n">
         <v>0.9341229519002309</v>
       </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>1.040852453731775</v>
+      </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>1.040852453731775</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19744,63 +19726,57 @@
         <v>3.52357110973727</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.128889306368128</v>
+        <v>78.88844621513944</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>78.88844621513944</v>
+        <v>1.312779800632722</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.312779800632722</v>
+        <v>1.238046916970095</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.238046916970095</v>
+        <v>373.6742781656916</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>1.348700353635984</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>266.9236343191207</v>
-      </c>
-      <c r="P3" s="3" t="n">
         <v>12.76398039075149</v>
       </c>
-      <c r="Q3" s="3" t="n">
-        <v>28.20436799329843</v>
-      </c>
-      <c r="R3" s="6" t="n">
+      <c r="P3" s="6" t="n">
         <v>0.7053523165834162</v>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="Q3" s="6" t="n">
         <v>0.8030464547899122</v>
       </c>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="3" t="n">
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="3" t="n">
         <v>-18.74603657828261</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>147.7874001681685</v>
       </c>
-      <c r="W3" s="6" t="n">
+      <c r="U3" s="6" t="n">
         <v>-0.3572846367606193</v>
       </c>
+      <c r="V3" s="6" t="n">
+        <v>-0.7301558464641208</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>-976000000</v>
+      </c>
       <c r="X3" s="6" t="n">
-        <v>-0.7301558464641208</v>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>-976000000</v>
-      </c>
-      <c r="Z3" s="6" t="n">
         <v>0.9285025938953059</v>
       </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>−/+/+</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>1.356300231530294</v>
+      </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>−/+/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>1.356300231530294</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19836,64 +19812,58 @@
       <c r="I4" s="3" t="n">
         <v>3.627183701302302</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>0.06568228661814815</v>
+      <c r="J4" s="3" t="n">
+        <v>80.78144361833954</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>80.78144361833954</v>
+        <v>1.27047913446677</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.27047913446677</v>
+        <v>1.182609193428359</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.182609193428359</v>
+        <v>420.245769540693</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>1.378543497703497</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>261.1451873660285</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>12.93338447655544</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>27.83494147665509</v>
-      </c>
-      <c r="R4" s="6" t="n">
+      <c r="P4" s="6" t="n">
         <v>0.7183455788048857</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="Q4" s="6" t="n">
         <v>0.8278686096603073</v>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="3" t="n">
+        <v>3.126006434253918</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-77.29100797025789</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>3.126006434253918</v>
+        <v>2.884462151394422</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-77.29100797025789</v>
+        <v>1.47386897879675</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>2.884462151394422</v>
+        <v>-489000000</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>1.47386897879675</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>-489000000</v>
+        <v>1.111395707461693</v>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.111395707461693</v>
+        <v>1.226425287601905</v>
       </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>1.226425287601905</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19929,64 +19899,58 @@
       <c r="I5" s="3" t="n">
         <v>3.873044195430306</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>0.05247191959413847</v>
+      <c r="J5" s="3" t="n">
+        <v>78.22922282985442</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>78.22922282985442</v>
+        <v>1.281259442799299</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.281259442799299</v>
+        <v>1.174351846256119</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.174351846256119</v>
+        <v>359.3313284981426</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>1.501077396772245</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>239.8277402445105</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>10.65008256070823</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>33.80255485794656</v>
-      </c>
-      <c r="R5" s="6" t="n">
+      <c r="P5" s="6" t="n">
         <v>0.6908897838744932</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>0.8245461898112686</v>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="3" t="n">
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="3" t="n">
         <v>-2.186511267241741</v>
       </c>
+      <c r="T5" s="3" t="n">
+        <v>14.06402162242492</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0.5498760842627162</v>
+      </c>
       <c r="V5" s="3" t="n">
-        <v>14.06402162242492</v>
-      </c>
-      <c r="W5" s="6" t="n">
-        <v>0.5498760842627162</v>
+        <v>6.644082604288533</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>828000000</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>6.644082604288533</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>828000000</v>
+        <v>1.082077168406138</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>1.082077168406138</v>
+        <v>1.235526188953743</v>
       </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>1.235526188953743</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20022,64 +19986,58 @@
       <c r="I6" s="3" t="n">
         <v>4.497326201136937</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>0.9375627572534658</v>
+      <c r="J6" s="3" t="n">
+        <v>73.36115678091143</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>73.36115678091143</v>
+        <v>1.268120085775554</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.268120085775554</v>
+        <v>1.131308077197999</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.131308077197999</v>
+        <v>275.3916758980851</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>1.582345983106224</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>227.5102941098268</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>7.565555344496334</v>
       </c>
-      <c r="Q6" s="3" t="n">
-        <v>47.58408122172906</v>
-      </c>
-      <c r="R6" s="6" t="n">
+      <c r="P6" s="6" t="n">
         <v>0.5618320251566808</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>0.7168544973026552</v>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="3" t="n">
+        <v>-21.9820409884002</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-74.08801654542918</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>-21.9820409884002</v>
+        <v>-8.645921589771252</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-74.08801654542918</v>
+        <v>2.79779463883675</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-8.645921589771252</v>
+        <v>-632000000</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>2.79779463883675</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>-632000000</v>
+        <v>1.173746094673473</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.173746094673473</v>
+        <v>1.150770019154872</v>
       </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>1.150770019154872</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20115,64 +20073,58 @@
       <c r="I7" s="3" t="n">
         <v>4.171014126364607</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>0.5999086837561255</v>
+      <c r="J7" s="3" t="n">
+        <v>80.55204140310522</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>80.55204140310522</v>
+        <v>1.260091145833333</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.260091145833333</v>
+        <v>1.094921875</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.094921875</v>
+        <v>414.1927853341218</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>2.85209321026822</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>126.2230837000395</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>7.226300266919794</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>49.81802398220158</v>
-      </c>
-      <c r="R7" s="6" t="n">
+      <c r="P7" s="6" t="n">
         <v>0.6191388946998353</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="Q7" s="6" t="n">
         <v>0.8312710747633167</v>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="3" t="n">
+        <v>10.46392872164596</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-1377.187816546908</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>10.46392872164596</v>
+        <v>9.965853041608717</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>-1377.187816546908</v>
+        <v>-2.431554708613784</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>9.965853041608717</v>
+        <v>1654000000</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-2.431554708613784</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>1654000000</v>
-      </c>
-      <c r="Z7" s="3" t="n">
         <v>1.13494149590321</v>
       </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="n">
+        <v>0.913869660198705</v>
+      </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB7" s="6" t="n">
-        <v>0.913869660198705</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20208,64 +20160,58 @@
       <c r="I8" s="3" t="n">
         <v>3.713542473496124</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>-0.7638277719668873</v>
+      <c r="J8" s="3" t="n">
+        <v>83.86655137627901</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>83.86655137627901</v>
-      </c>
-      <c r="L8" s="3" t="n">
         <v>1.078391905124578</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="L8" s="6" t="n">
         <v>0.9317266891524317</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>519.8302813756142</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>3.937912123311745</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>91.41900294546025</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>7.090762007983948</v>
       </c>
-      <c r="Q8" s="3" t="n">
-        <v>50.77028387000617</v>
-      </c>
-      <c r="R8" s="6" t="n">
+      <c r="P8" s="6" t="n">
         <v>0.6775657567719767</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>0.9311556973393231</v>
       </c>
-      <c r="T8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>18.30274315948512</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>41.13847858731506</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>18.30274315948512</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>41.13847858731506</v>
+        <v>6.405980448533624</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0.4006191929264498</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>6.405980448533624</v>
+        <v>-542000000</v>
       </c>
       <c r="X8" s="6" t="n">
-        <v>0.4006191929264498</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>-542000000</v>
+        <v>0.9328189977433591</v>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>0.9328189977433591</v>
+        <v>0.8455817677407147</v>
       </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB8" s="6" t="n">
-        <v>0.8455817677407147</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20301,64 +20247,58 @@
       <c r="I9" s="3" t="n">
         <v>3.860455945062697</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.4516858318980501</v>
-      </c>
-      <c r="K9" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>84.48727189954096</v>
       </c>
+      <c r="K9" s="6" t="n">
+        <v>0.9987927565392354</v>
+      </c>
       <c r="L9" s="6" t="n">
-        <v>0.9987927565392354</v>
-      </c>
-      <c r="M9" s="6" t="n">
         <v>0.8711123886174188</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>544.4987775061124</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>4.64222258070591</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>77.54906055048686</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>8.001006593906853</v>
       </c>
+      <c r="P9" s="6" t="n">
+        <v>0.716985980403585</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>44.99433862161258</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0.716985980403585</v>
-      </c>
+        <v>1.043086709399683</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>1.043086709399683</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>6.356432097761367</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>131.535685359473</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>6.356432097761367</v>
+        <v>-5.033145986453393</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>131.535685359473</v>
+        <v>16.45230432014899</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>-5.033145986453393</v>
+        <v>2147000000</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>16.45230432014899</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>2147000000</v>
-      </c>
-      <c r="Z9" s="3" t="n">
         <v>1.111091170246566</v>
       </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z9" s="6" t="n">
+        <v>0.9446291316859271</v>
+      </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB9" s="6" t="n">
-        <v>0.9446291316859271</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20394,64 +20334,58 @@
       <c r="I10" s="3" t="n">
         <v>3.584757847261888</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>0.0487031681135803</v>
+      <c r="J10" s="3" t="n">
+        <v>84.24614934328467</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>84.24614934328467</v>
-      </c>
-      <c r="L10" s="3" t="n">
         <v>1.103186034452958</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>0.9843290891283056</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>534.7654435671157</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>5.874301221355672</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>61.28388491404586</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>10.71723544452381</v>
       </c>
+      <c r="P10" s="6" t="n">
+        <v>0.8554563296167027</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>33.59075219197031</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0.8554563296167027</v>
-      </c>
+        <v>1.257629955910958</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>1.257629955910958</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>18.38020808119182</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>89.45448164212169</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>18.38020808119182</v>
+        <v>3.695132592283486</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>89.45448164212169</v>
+        <v>4.583854402158065</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>3.695132592283486</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>4.583854402158065</v>
-      </c>
-      <c r="Y10" s="3" t="n">
         <v>964000000</v>
       </c>
-      <c r="Z10" s="6" t="n">
+      <c r="X10" s="6" t="n">
         <v>0.9818171100608958</v>
       </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>1.143439709983081</v>
+      </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>1.143439709983081</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20487,64 +20421,58 @@
       <c r="I11" s="3" t="n">
         <v>3.733322033502398</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.04096843882492649</v>
+      <c r="J11" s="3" t="n">
+        <v>84.80613638751707</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>84.80613638751707</v>
-      </c>
-      <c r="L11" s="3" t="n">
         <v>1.022109885620915</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>0.8767871732026143</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>558.1604426002766</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>5.153096273414506</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>69.86091097449253</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>9.765823542949683</v>
       </c>
+      <c r="P11" s="6" t="n">
+        <v>0.8784902332835874</v>
+      </c>
       <c r="Q11" s="3" t="n">
-        <v>36.86325054069788</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0.8784902332835874</v>
-      </c>
+        <v>1.253505635052215</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.253505635052215</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>6.885057684134098</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>114.7067413235449</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>6.885057684134098</v>
+        <v>4.456151904291516</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>114.7067413235449</v>
+        <v>2.839756787867378</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>4.456151904291516</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>2.839756787867378</v>
-      </c>
-      <c r="Y11" s="3" t="n">
         <v>1332000000</v>
       </c>
-      <c r="Z11" s="6" t="n">
+      <c r="X11" s="6" t="n">
         <v>0.9944687600144251</v>
       </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>1.138960051112933</v>
+      </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>1.138960051112933</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
